--- a/Loyola/HChem2627/build/Honors_Chem_2627_Schedule_2.xlsx
+++ b/Loyola/HChem2627/build/Honors_Chem_2627_Schedule_2.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -105,7 +106,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -135,6 +136,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -400,7 +404,7 @@
     <row r="1" ht="19.5" customHeight="1" s="6">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Assignments</t>
+          <t>School Day #</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr">
@@ -420,10 +424,8 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="6">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Introduction</t>
-        </is>
+      <c r="A2" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>46252</v>
@@ -436,13 +438,8 @@
       </c>
     </row>
     <row r="3" ht="55.5" customHeight="1" s="6">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>1.2, Material Classification, Classwork
-Chemistry definition
-Matter definitions
-Properties definitions</t>
-        </is>
+      <c r="A3" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="9" t="n">
         <v>46253</v>
@@ -455,12 +452,8 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>1.5 to 1.6, units and sig figs, classwork
-Counting Sig Figs
-Accuracy/Precision/Temperature Scales</t>
-        </is>
+      <c r="A4" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>46255</v>
@@ -473,12 +466,8 @@
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" s="6">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>1.6, operations with sig figs, classwork
-Adding / Subtracting with Sig Figs
-Multiplying / Dividing with Sig Figs</t>
-        </is>
+      <c r="A5" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>46258</v>
@@ -491,10 +480,8 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Lab #1</t>
-        </is>
+      <c r="A6" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>46260</v>
@@ -507,14 +494,8 @@
       </c>
     </row>
     <row r="7" ht="69.75" customHeight="1" s="6">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Quiz #1 on sections 1.1 - 1.5
-Post-Lab Quiz #1
-1.7, Dimensional analysis part 1, classwork
-Dimensional analysis, section 1.7
-Homework 1 part 1 due</t>
-        </is>
+      <c r="A7" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>46261</v>
@@ -527,12 +508,8 @@
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" s="6">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>1.7, Dimensional analysis part 2, classwork
-Dimensional analysis, part 2
-Lab #1 due</t>
-        </is>
+      <c r="A8" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>46265</v>
@@ -545,12 +522,8 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" s="6">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>1.7, Dimensional analysis part 3, classwork
-Dimensional analysis, part 3
-atomic structure part 1</t>
-        </is>
+      <c r="A9" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>46266</v>
@@ -563,10 +536,8 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="6">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Lab #2</t>
-        </is>
+      <c r="A10" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>46268</v>
@@ -579,14 +550,8 @@
       </c>
     </row>
     <row r="11" ht="69.75" customHeight="1" s="6">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2.3, atomic structure part 2, classwork
-2.2, atomic structure part 1, classwork
-atomic structure part 2
-Quiz #2 Dimensional analysis
-Post Lab Quiz #2</t>
-        </is>
+      <c r="A11" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>46273</v>
@@ -599,13 +564,8 @@
       </c>
     </row>
     <row r="12" ht="55.5" customHeight="1" s="6">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2.4, atomic weight part 3, classwork
-atomic weight
-Lab 2 due
-Homework 1 part 2 due</t>
-        </is>
+      <c r="A12" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>46275</v>
@@ -618,12 +578,8 @@
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" s="6">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>2.8, Nomenclature part 1
-2.8, Nomenclature part 2
-2.8 Naming Inorganic Compounds part 2</t>
-        </is>
+      <c r="A13" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>46279</v>
@@ -636,12 +592,8 @@
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" s="6">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>2.8, Nomenclature part 3
-2.8 Naming Inorganic Compounds part 3
-Quiz #3 inorganic nomenclature</t>
-        </is>
+      <c r="A14" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>46280</v>
@@ -654,11 +606,8 @@
       </c>
     </row>
     <row r="15" ht="27.75" customHeight="1" s="6">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Exam 1 part 1
-Exam 1 Review - Build On</t>
-        </is>
+      <c r="A15" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -675,12 +624,8 @@
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" s="6">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Exam 1 part 2
-3.1 Balancing Equations, Classwork
-Homework 2 Due</t>
-        </is>
+      <c r="A16" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>46283</v>
@@ -693,10 +638,8 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="6">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>3.2 Types of Reactions, Classwork</t>
-        </is>
+      <c r="A17" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>46287</v>
@@ -709,11 +652,8 @@
       </c>
     </row>
     <row r="18" ht="27.75" customHeight="1" s="6">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>3.3 Classwork
-3.3 molar mass and composition</t>
-        </is>
+      <c r="A18" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>46288</v>
@@ -726,10 +666,8 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="6">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Lab 3 - sync</t>
-        </is>
+      <c r="A19" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>46290</v>
@@ -742,10 +680,8 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="6">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>3.4 Classwork</t>
-        </is>
+      <c r="A20" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>46294</v>
@@ -758,11 +694,8 @@
       </c>
     </row>
     <row r="21" ht="27.75" customHeight="1" s="6">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>3.5 Part 1 and Part 2
-Lab 3 Due</t>
-        </is>
+      <c r="A21" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>46295</v>
@@ -777,10 +710,8 @@
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="6">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>3.6, stoichiometry</t>
-        </is>
+      <c r="A22" s="8" t="n">
+        <v>21</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>46297</v>
@@ -793,11 +724,8 @@
       </c>
     </row>
     <row r="23" ht="27.75" customHeight="1" s="6">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>3.7 classwork, part 1
-3.7 part 1, limiting reagent</t>
-        </is>
+      <c r="A23" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>46300</v>
@@ -810,11 +738,8 @@
       </c>
     </row>
     <row r="24" ht="27.75" customHeight="1" s="6">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>3.7 classwork, part 2
-3.7 part 2, excess reagent and % yield</t>
-        </is>
+      <c r="A24" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>46302</v>
@@ -829,10 +754,8 @@
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="6">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Lab 4</t>
-        </is>
+      <c r="A25" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -847,11 +770,8 @@
       </c>
     </row>
     <row r="26" ht="27.75" customHeight="1" s="6">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Post-Lab Quiz #4
-quiz #4 (3.1 - 3.5)</t>
-        </is>
+      <c r="A26" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -866,10 +786,8 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="6">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Chapter 3 exam #2 part 1</t>
-        </is>
+      <c r="A27" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>46310</v>
@@ -886,14 +804,8 @@
       </c>
     </row>
     <row r="28" ht="67.5" customHeight="1" s="6">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Chapter 3 exam #2 part 2
-4.2, part 1, classwork
-4.1 and 4.3 Classwork
-Lab 4 due
-Homework #3 due</t>
-        </is>
+      <c r="A28" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>46314</v>
@@ -906,10 +818,8 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="6">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>4.2 part 2, double displacement reactions</t>
-        </is>
+      <c r="A29" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>46315</v>
@@ -922,11 +832,8 @@
       </c>
     </row>
     <row r="30" ht="27.75" customHeight="1" s="6">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>4.3 Classwork
-Quiz #5</t>
-        </is>
+      <c r="A30" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -941,10 +848,8 @@
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="6">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>4.5 and 4.6 Classwork</t>
-        </is>
+      <c r="A31" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>46318</v>
@@ -957,10 +862,8 @@
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="6">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>5.1 to 5.3 Classwork</t>
-        </is>
+      <c r="A32" s="8" t="n">
+        <v>31</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>46322</v>
@@ -975,12 +878,8 @@
       </c>
     </row>
     <row r="33" ht="42" customHeight="1" s="6">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>5.4 Classwork
-homework #4 due
-Quiz #6</t>
-        </is>
+      <c r="A33" s="8" t="n">
+        <v>32</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>46323</v>
@@ -993,10 +892,8 @@
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="6">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>5.5 Classwork</t>
-        </is>
+      <c r="A34" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="B34" s="9" t="n">
         <v>46328</v>
@@ -1009,10 +906,8 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="6">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>5.6 Classwork</t>
-        </is>
+      <c r="A35" s="8" t="n">
+        <v>34</v>
       </c>
       <c r="B35" s="9" t="n">
         <v>46329</v>
@@ -1025,10 +920,8 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="6">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>5.7 Classwork *rotated</t>
-        </is>
+      <c r="A36" s="8" t="n">
+        <v>35</v>
       </c>
       <c r="B36" s="9" t="n">
         <v>46331</v>
@@ -1041,10 +934,8 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="6">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Lab #5</t>
-        </is>
+      <c r="A37" s="8" t="n">
+        <v>36</v>
       </c>
       <c r="B37" s="9" t="n">
         <v>46332</v>
@@ -1059,10 +950,8 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="6">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Exam #3 part 1</t>
-        </is>
+      <c r="A38" s="8" t="n">
+        <v>37</v>
       </c>
       <c r="B38" s="9" t="n">
         <v>46337</v>
@@ -1077,12 +966,8 @@
       </c>
     </row>
     <row r="39" ht="42" customHeight="1" s="6">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Exam #3 part 2
-Post-Lab Quiz #5
-Homework #5 due</t>
-        </is>
+      <c r="A39" s="8" t="n">
+        <v>38</v>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
@@ -1101,11 +986,8 @@
       </c>
     </row>
     <row r="40" ht="27.75" customHeight="1" s="6">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>6.1 - 6.4 Classwork
-Lab 5 Due</t>
-        </is>
+      <c r="A40" s="8" t="n">
+        <v>39</v>
       </c>
       <c r="B40" s="9" t="n">
         <v>46342</v>
@@ -1118,10 +1000,8 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="6">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>6.5 Classwork</t>
-        </is>
+      <c r="A41" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
@@ -1136,10 +1016,8 @@
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="6">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>6.6 - 6.9 Electron configurations</t>
-        </is>
+      <c r="A42" s="8" t="n">
+        <v>41</v>
       </c>
       <c r="B42" s="9" t="n">
         <v>46345</v>
@@ -1152,7 +1030,9 @@
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="6">
-      <c r="A43" s="8" t="n"/>
+      <c r="A43" s="8" t="n">
+        <v>42</v>
+      </c>
       <c r="B43" s="9" t="n">
         <v>46356</v>
       </c>
@@ -1164,14 +1044,8 @@
       </c>
     </row>
     <row r="44" ht="69.75" customHeight="1" s="6">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>7.2-7.4 Classwork
-Periodic Properties
-7.2 Effective Nuclear Charge
-7.3 Atomic radius and ionic Radius
-7.4 Ionization Energy</t>
-        </is>
+      <c r="A44" s="8" t="n">
+        <v>43</v>
       </c>
       <c r="B44" s="9" t="n">
         <v>46357</v>
@@ -1184,11 +1058,8 @@
       </c>
     </row>
     <row r="45" ht="27.75" customHeight="1" s="6">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>8.1, 8.3, 8.5 Classwork
-8.1, 8.3, 8.5 Lewis dot symbols</t>
-        </is>
+      <c r="A45" s="8" t="n">
+        <v>44</v>
       </c>
       <c r="B45" s="9" t="n">
         <v>46359</v>
@@ -1201,12 +1072,8 @@
       </c>
     </row>
     <row r="46" ht="42" customHeight="1" s="6">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>8.2, 8.6-8.8 Classwork
-Lewis structures and resonance
-Quiz #7 - Chapter 6</t>
-        </is>
+      <c r="A46" s="8" t="n">
+        <v>45</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
@@ -1221,10 +1088,8 @@
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="6">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>8.4 - 8.7 Electronegativity, bond polarity, formal charge</t>
-        </is>
+      <c r="A47" s="8" t="n">
+        <v>46</v>
       </c>
       <c r="B47" s="9" t="n">
         <v>46364</v>
@@ -1237,13 +1102,8 @@
       </c>
     </row>
     <row r="48" ht="55.5" customHeight="1" s="6">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>9.1 - 9.2 Classwork
-9.1 - 9.2 Molecular Geometry
-9.3 Classwork
-9.3 Molecular Geometry</t>
-        </is>
+      <c r="A48" s="8" t="n">
+        <v>47</v>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
@@ -1258,10 +1118,8 @@
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="6">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>Lab #6</t>
-        </is>
+      <c r="A49" s="8" t="n">
+        <v>48</v>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
@@ -1276,40 +1134,28 @@
       </c>
     </row>
     <row r="50" ht="55.5" customHeight="1" s="6">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Homework 6-9 due
-Quiz #8, Chapter 8-9
-Post-Lab Quiz #6
-Lab 6 Due</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
+      <c r="A50" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>46371</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>46371</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>46371</v>
+      </c>
     </row>
     <row r="51" ht="69.75" customHeight="1" s="6">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>10.1 - 10.2
-Gas Pressure
-Units
-10.2 Classwork
-10.2 Classwork, Practice Version</t>
-        </is>
-      </c>
+      <c r="A51" s="8" t="n"/>
       <c r="B51" s="10" t="n"/>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="10" t="n"/>
     </row>
     <row r="52" ht="55.5" customHeight="1" s="6">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>10.3
-Combined Gas Law
-10.3 Classwork
-10.3 Classwork, Practice Version</t>
-        </is>
+      <c r="A52" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
@@ -1328,14 +1174,8 @@
       </c>
     </row>
     <row r="53" ht="69.75" customHeight="1" s="6">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>10.4 - 10.5
-Ideal Gas Law
-Molar mass and density
-10.4 - 10.5 Classwork
-10.4 - 10.5 Classwork, Practice Version</t>
-        </is>
+      <c r="A53" s="8" t="n">
+        <v>51</v>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
@@ -1354,14 +1194,8 @@
       </c>
     </row>
     <row r="54" ht="69.75" customHeight="1" s="6">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>10.6
-Gas Stoichiometry
-Dalton's Law of Partial Pressures
-10.6 Classwork
-10.6 Classwork, Practice Version</t>
-        </is>
+      <c r="A54" s="8" t="n">
+        <v>52</v>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
@@ -1380,15 +1214,8 @@
       </c>
     </row>
     <row r="55" ht="84" customHeight="1" s="6">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>10.7-10.8
-Effusion and Diffusion
-Graham's Law
-Kinetic Molecular Theory
-10.7 - 10.8 Classwork
-10.7 - 10.8 Classwork, Practice Version</t>
-        </is>
+      <c r="A55" s="8" t="n">
+        <v>53</v>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
@@ -1407,10 +1234,8 @@
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="6">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Introduction to Data Science /Programming in Snap!</t>
-        </is>
+      <c r="A56" s="8" t="n">
+        <v>54</v>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
@@ -1429,10 +1254,8 @@
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="6">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Introduction to Data Science /Programming in Snap!</t>
-        </is>
+      <c r="A57" s="8" t="n">
+        <v>55</v>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
@@ -1451,12 +1274,8 @@
       </c>
     </row>
     <row r="58" ht="42" customHeight="1" s="6">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>11.1 - 11.3
-11.1 - 11.3 Classwork
-11.1 - 11.3 Classwork, Practice version</t>
-        </is>
+      <c r="A58" s="8" t="n">
+        <v>56</v>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
@@ -1475,12 +1294,8 @@
       </c>
     </row>
     <row r="59" ht="42" customHeight="1" s="6">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>11.4
-Homework 11.4
-Homework 11.4, Practice Version</t>
-        </is>
+      <c r="A59" s="8" t="n">
+        <v>57</v>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
@@ -1499,14 +1314,8 @@
       </c>
     </row>
     <row r="60" ht="69.75" customHeight="1" s="6">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>SNAP Quiz
-Chapter 10 Quiz #9
-11.5 - 11.6
-11.5 and 11.6 Classwork
-11.5 and 11.6 Classwork, Practice Version</t>
-        </is>
+      <c r="A60" s="8" t="n">
+        <v>58</v>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
@@ -1525,10 +1334,8 @@
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="6">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>Lab #8</t>
-        </is>
+      <c r="A61" s="8" t="n">
+        <v>59</v>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
@@ -1547,12 +1354,8 @@
       </c>
     </row>
     <row r="62" ht="42" customHeight="1" s="6">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>12.1 - 12.7
-Post-Lab #8
-Homework 10 Due</t>
-        </is>
+      <c r="A62" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
@@ -1571,12 +1374,8 @@
       </c>
     </row>
     <row r="63" ht="42" customHeight="1" s="6">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>13.1 - 13.2
-13.1 - 13.4 Classwork
-13.1 - 13.4 Classwork, Practice Version</t>
-        </is>
+      <c r="A63" s="8" t="n">
+        <v>61</v>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
@@ -1595,10 +1394,8 @@
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="6">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>13.3-13.4</t>
-        </is>
+      <c r="A64" s="8" t="n">
+        <v>62</v>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
@@ -1617,12 +1414,8 @@
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" s="6">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>13.5-13.6
-13.5 Classwork
-13.5 Classwork, Practice Version</t>
-        </is>
+      <c r="A65" s="8" t="n">
+        <v>63</v>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
@@ -1641,10 +1434,8 @@
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="6">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>Multiple Choice Exam (10 - 13)</t>
-        </is>
+      <c r="A66" s="8" t="n">
+        <v>64</v>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
@@ -1663,10 +1454,8 @@
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="6">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>Ice Cream Lab</t>
-        </is>
+      <c r="A67" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
@@ -1685,15 +1474,8 @@
       </c>
     </row>
     <row r="68" ht="84" customHeight="1" s="6">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>Ch. 10 - 13 Free Response Exam
-Homework 11 and 12 due
-Homework 13 due
-14.1
-Calculating rates with concentration and time data
-Calculating relative rates using balanced chemical equations</t>
-        </is>
+      <c r="A68" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
@@ -1712,10 +1494,8 @@
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="6">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>14.3 Rate Laws</t>
-        </is>
+      <c r="A69" s="8" t="n">
+        <v>67</v>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
@@ -1734,12 +1514,8 @@
       </c>
     </row>
     <row r="70" ht="42" customHeight="1" s="6">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>14.4-14.7
-Energy Diagrams
-Collision Theory</t>
-        </is>
+      <c r="A70" s="8" t="n">
+        <v>68</v>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
@@ -1758,7 +1534,9 @@
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="6">
-      <c r="A71" s="8" t="n"/>
+      <c r="A71" s="8" t="n">
+        <v>69</v>
+      </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
           <t>2027-03-03</t>
@@ -1776,11 +1554,8 @@
       </c>
     </row>
     <row r="72" ht="27.75" customHeight="1" s="6">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>14.6-14.7
-Mechanisms (intermediates/catalysts)</t>
-        </is>
+      <c r="A72" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
@@ -1799,10 +1574,8 @@
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="6">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>Kinetics Lab (Factors that influence reaction rates)</t>
-        </is>
+      <c r="A73" s="8" t="n">
+        <v>71</v>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
@@ -1821,10 +1594,8 @@
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="6">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Multiple Choice and Free Response Exam Ch. 14</t>
-        </is>
+      <c r="A74" s="8" t="n">
+        <v>72</v>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
@@ -1843,14 +1614,8 @@
       </c>
     </row>
     <row r="75" ht="69.75" customHeight="1" s="6">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>15.1 - 15.2
-Equilibrium condition
-Equilibrium constant
-Kc and Kp
-Post Lab Quiz #9</t>
-        </is>
+      <c r="A75" s="8" t="n">
+        <v>73</v>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
@@ -1869,10 +1634,8 @@
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="6">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>15.3 - 15.4</t>
-        </is>
+      <c r="A76" s="8" t="n">
+        <v>74</v>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
@@ -1891,12 +1654,8 @@
       </c>
     </row>
     <row r="77" ht="42" customHeight="1" s="6">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>15.5 - 15.6
-Chapter 14 Quiz #11
-Homework #14 due</t>
-        </is>
+      <c r="A77" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
@@ -1915,10 +1674,8 @@
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="6">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>Equilibrium Worksheet</t>
-        </is>
+      <c r="A78" s="8" t="n">
+        <v>76</v>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
@@ -1937,10 +1694,8 @@
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="6">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>15.7</t>
-        </is>
+      <c r="A79" s="8" t="n">
+        <v>77</v>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
@@ -1959,12 +1714,8 @@
       </c>
     </row>
     <row r="80" ht="42" customHeight="1" s="6">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>16.1 Acids and Bases
-16.2 Definitions of Acids and Bases
-Bronsted Lowry Acids and Bases</t>
-        </is>
+      <c r="A80" s="8" t="n">
+        <v>78</v>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
@@ -1983,10 +1734,8 @@
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="6">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>Equilibrium Lab</t>
-        </is>
+      <c r="A81" s="8" t="n">
+        <v>79</v>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
@@ -2005,10 +1754,8 @@
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="6">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>Equilibrium Programming Project</t>
-        </is>
+      <c r="A82" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
@@ -2027,11 +1774,8 @@
       </c>
     </row>
     <row r="83" ht="27.75" customHeight="1" s="6">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>16.11 Lewis Acids and Bases
-16.3 Autoionization of water</t>
-        </is>
+      <c r="A83" s="8" t="n">
+        <v>81</v>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
@@ -2050,10 +1794,8 @@
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="6">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>16.4 pH scale and calculations</t>
-        </is>
+      <c r="A84" s="8" t="n">
+        <v>82</v>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
@@ -2072,13 +1814,8 @@
       </c>
     </row>
     <row r="85" ht="55.5" customHeight="1" s="6">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>16.5 Strong Acids
-16.5 Strong Bases
-16.10 Acid base structures and behavior
-Homework #15 due</t>
-        </is>
+      <c r="A85" s="8" t="n">
+        <v>83</v>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
@@ -2097,10 +1834,8 @@
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="6">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>16.6 Weak Acids</t>
-        </is>
+      <c r="A86" s="8" t="n">
+        <v>84</v>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
@@ -2119,10 +1854,8 @@
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="6">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>16.7 Weak Bases (VIDEO, NSTA Conference)</t>
-        </is>
+      <c r="A87" s="8" t="n">
+        <v>85</v>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
@@ -2141,10 +1874,8 @@
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="6">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>Titration Lab</t>
-        </is>
+      <c r="A88" s="8" t="n">
+        <v>86</v>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
@@ -2163,10 +1894,8 @@
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="6">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>16.7 Weak Bases</t>
-        </is>
+      <c r="A89" s="8" t="n">
+        <v>87</v>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
@@ -2185,10 +1914,8 @@
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="6">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Exam 6 (chapter 15 &amp; 16) MC</t>
-        </is>
+      <c r="A90" s="8" t="n">
+        <v>88</v>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
@@ -2207,13 +1934,8 @@
       </c>
     </row>
     <row r="91" ht="55.5" customHeight="1" s="6">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>Entropy programming
-Entropy Snap.pdf
-Post Lab Quiz #10
-Exam 6 (chapter 15 and 16) Free Response</t>
-        </is>
+      <c r="A91" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
@@ -2232,12 +1954,8 @@
       </c>
     </row>
     <row r="92" ht="42" customHeight="1" s="6">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>19.1 - 19.3 Enthalpy, Entropy and Gibbs Free Energy
-Chapter 16 Homework due
-Chapter 15 Homework due</t>
-        </is>
+      <c r="A92" s="8" t="n">
+        <v>90</v>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
@@ -2256,10 +1974,8 @@
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="6">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>19.4 to 19.6 Classwork</t>
-        </is>
+      <c r="A93" s="8" t="n">
+        <v>91</v>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
@@ -2278,11 +1994,8 @@
       </c>
     </row>
     <row r="94" ht="27.75" customHeight="1" s="6">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>20.1 Oxidation States
-19.5 - 19.7 Gibbs Free Energy</t>
-        </is>
+      <c r="A94" s="8" t="n">
+        <v>92</v>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
@@ -2301,10 +2014,8 @@
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="6">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>20.2 Balancing Redox Reactions</t>
-        </is>
+      <c r="A95" s="8" t="n">
+        <v>93</v>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
@@ -2323,10 +2034,8 @@
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="6">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>AP World History Exam</t>
-        </is>
+      <c r="A96" s="8" t="n">
+        <v>94</v>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
@@ -2345,11 +2054,8 @@
       </c>
     </row>
     <row r="97" ht="27.75" customHeight="1" s="6">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>20.2 Balancing Redox Reactions
-Chapter 19 quiz #13</t>
-        </is>
+      <c r="A97" s="8" t="n">
+        <v>95</v>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
@@ -2368,13 +2074,8 @@
       </c>
     </row>
     <row r="98" ht="55.5" customHeight="1" s="6">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>20.3 - 20.4, Classwork
-Voltaic Cells
-Cell Potential
-Free Energy</t>
-        </is>
+      <c r="A98" s="8" t="n">
+        <v>96</v>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
@@ -2393,12 +2094,8 @@
       </c>
     </row>
     <row r="99" ht="42" customHeight="1" s="6">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>20.4 - 20.5 Classwork
-Cell Potential
-Free Energy</t>
-        </is>
+      <c r="A99" s="8" t="n">
+        <v>97</v>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
@@ -2417,10 +2114,8 @@
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="6">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A100" s="8" t="n">
+        <v>98</v>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
@@ -2439,10 +2134,8 @@
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="6">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>Lab #11</t>
-        </is>
+      <c r="A101" s="8" t="n">
+        <v>99</v>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
@@ -2461,10 +2154,8 @@
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="6">
-      <c r="A102" s="8" t="inlineStr">
-        <is>
-          <t>Post-lab# 11 quiz</t>
-        </is>
+      <c r="A102" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
@@ -2483,11 +2174,8 @@
       </c>
     </row>
     <row r="103" ht="27.75" customHeight="1" s="6">
-      <c r="A103" s="8" t="inlineStr">
-        <is>
-          <t>Exam on Chapter 16, 19, 20, and 21
-Ch 19/20 Homework due</t>
-        </is>
+      <c r="A103" s="8" t="n">
+        <v>101</v>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
@@ -2506,10 +2194,8 @@
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="6">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>Organic Day 1 (24.1 - 24.3)</t>
-        </is>
+      <c r="A104" s="8" t="n">
+        <v>102</v>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
@@ -2528,11 +2214,8 @@
       </c>
     </row>
     <row r="105" ht="27.75" customHeight="1" s="6">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>Organic Day 2 (24.1 - 24.3)
-Final Exam Review</t>
-        </is>
+      <c r="A105" s="8" t="n">
+        <v>103</v>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
@@ -2551,10 +2234,8 @@
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="6">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>Final Exam Review</t>
-        </is>
+      <c r="A106" s="8" t="n">
+        <v>104</v>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
@@ -2573,6 +2254,9 @@
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="6">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
           <t>2027-06-03</t>
@@ -2590,6 +2274,9 @@
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="6">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
           <t>2027-06-04</t>
